--- a/รายงานปฏิบัติงาน.xlsx
+++ b/รายงานปฏิบัติงาน.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF0332F0-F399-436A-BCA7-8F0C4164CBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78381EE8-E96A-48FD-BEEA-7977A83D9061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E913D3C6-8093-4C01-A734-76B2ECFA7B3E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E913D3C6-8093-4C01-A734-76B2ECFA7B3E}"/>
   </bookViews>
   <sheets>
     <sheet name="ก.ค.69  " sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>รายงานแสดงเวลาปฏิบัติงาน</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>[SHIFT_1]</t>
+  </si>
+  <si>
+    <t>ย</t>
+  </si>
+  <si>
+    <t>[1_2]</t>
   </si>
 </sst>
 </file>
@@ -214,12 +220,9 @@
       <charset val="222"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="TH SarabunPSK"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="222"/>
     </font>
   </fonts>
   <fills count="2">
@@ -360,11 +363,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -374,21 +374,102 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -402,102 +483,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -900,146 +885,148 @@
   <dimension ref="A1:R46"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="5.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="5.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="2" customWidth="1"/>
-    <col min="11" max="17" width="5.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="4.109375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="4" width="5.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="1" customWidth="1"/>
+    <col min="11" max="17" width="5.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+    </row>
+    <row r="2" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="35">
         <v>2569</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-    </row>
-    <row r="4" spans="1:18" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="36"/>
+      <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="11" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="37"/>
+      <c r="L4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="12" t="s">
+      <c r="M4" s="2"/>
+      <c r="N4" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="3" t="s">
+      <c r="O4" s="38"/>
+      <c r="P4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="13"/>
+      <c r="R4" s="39"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="40"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
@@ -1059,11 +1046,11 @@
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="15" t="s">
         <v>16</v>
       </c>
@@ -1087,28 +1074,28 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
       <c r="R7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="9">
         <v>1</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="21"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
       <c r="H8" s="15" t="s">
         <v>11</v>
       </c>
@@ -1118,27 +1105,27 @@
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
-      <c r="O8" s="22" t="s">
+      <c r="O8" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23">
+      <c r="A9" s="8">
         <v>2</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="19" t="s">
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
       <c r="H9" s="15" t="s">
         <v>11</v>
       </c>
@@ -1148,27 +1135,27 @@
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
     </row>
     <row r="10" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="19" t="s">
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="21"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
       <c r="H10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1178,27 +1165,27 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
-      <c r="O10" s="22" t="s">
+      <c r="O10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23">
+      <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24" t="s">
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="25"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="15" t="s">
         <v>11</v>
       </c>
@@ -1208,25 +1195,25 @@
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
     </row>
     <row r="12" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>6</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="26">
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="27">
         <v>18</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="15" t="s">
         <v>11</v>
       </c>
@@ -1236,25 +1223,25 @@
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
     </row>
     <row r="13" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23">
+      <c r="A13" s="8">
         <v>6</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <v>6</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="26">
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="27">
         <v>18</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="15" t="s">
         <v>11</v>
       </c>
@@ -1264,25 +1251,25 @@
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23">
+      <c r="A14" s="8">
         <v>7</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <v>6</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="26">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="27">
         <v>18</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="15" t="s">
         <v>11</v>
       </c>
@@ -1292,25 +1279,25 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23">
+      <c r="A15" s="8">
         <v>8</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="24">
         <v>6</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30">
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24">
         <v>18</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="15" t="s">
         <v>11</v>
       </c>
@@ -1320,25 +1307,25 @@
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23">
+      <c r="A16" s="8">
         <v>9</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="24">
         <v>0</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30">
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24">
         <v>12</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="15" t="s">
         <v>11</v>
       </c>
@@ -1348,25 +1335,25 @@
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="34"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="21"/>
     </row>
     <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
+      <c r="A17" s="8">
         <v>10</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="19" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="15" t="s">
         <v>11</v>
       </c>
@@ -1376,25 +1363,25 @@
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="34"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="21"/>
     </row>
     <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23">
+      <c r="A18" s="8">
         <v>11</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
       <c r="H18" s="15" t="s">
         <v>11</v>
       </c>
@@ -1404,21 +1391,23 @@
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="34"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="21"/>
     </row>
     <row r="19" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23">
+      <c r="A19" s="8">
         <v>12</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="37"/>
+      <c r="B19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
@@ -1426,21 +1415,21 @@
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="34"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="21"/>
     </row>
     <row r="20" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23">
+      <c r="A20" s="8">
         <v>13</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="37"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
@@ -1448,21 +1437,21 @@
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
     </row>
     <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23">
+      <c r="A21" s="8">
         <v>14</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -1470,21 +1459,21 @@
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23">
+      <c r="A22" s="8">
         <v>15</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="37"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
@@ -1492,21 +1481,21 @@
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="34"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="21"/>
     </row>
     <row r="23" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23">
+      <c r="A23" s="8">
         <v>16</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
@@ -1516,21 +1505,21 @@
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="34"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="21"/>
     </row>
     <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23">
+      <c r="A24" s="8">
         <v>17</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="37"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
@@ -1540,21 +1529,21 @@
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
     </row>
     <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23">
+      <c r="A25" s="8">
         <v>18</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="37"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
@@ -1562,21 +1551,21 @@
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
     </row>
     <row r="26" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23">
+      <c r="A26" s="8">
         <v>19</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
@@ -1584,21 +1573,21 @@
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="34"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="21"/>
     </row>
     <row r="27" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23">
+      <c r="A27" s="8">
         <v>20</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
@@ -1606,21 +1595,21 @@
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="34"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="21"/>
     </row>
     <row r="28" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23">
+      <c r="A28" s="8">
         <v>21</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="37"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
@@ -1628,21 +1617,21 @@
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
     </row>
     <row r="29" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="23">
+      <c r="A29" s="8">
         <v>22</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="37"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
       <c r="J29" s="15"/>
@@ -1650,21 +1639,21 @@
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="34"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="21"/>
     </row>
     <row r="30" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23">
+      <c r="A30" s="8">
         <v>23</v>
       </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="37"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="18"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
@@ -1672,21 +1661,21 @@
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="32"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="34"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="21"/>
     </row>
     <row r="31" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23">
+      <c r="A31" s="8">
         <v>24</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="37"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
@@ -1694,21 +1683,21 @@
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="38"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
     </row>
     <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="23">
+      <c r="A32" s="8">
         <v>25</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
@@ -1722,15 +1711,15 @@
       <c r="R32" s="15"/>
     </row>
     <row r="33" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="23">
+      <c r="A33" s="8">
         <v>26</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
@@ -1744,15 +1733,15 @@
       <c r="R33" s="15"/>
     </row>
     <row r="34" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="23">
+      <c r="A34" s="8">
         <v>27</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="37"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="18"/>
       <c r="H34" s="15"/>
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
@@ -1766,15 +1755,15 @@
       <c r="R34" s="15"/>
     </row>
     <row r="35" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23">
+      <c r="A35" s="8">
         <v>28</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="37"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="18"/>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
       <c r="J35" s="15"/>
@@ -1788,15 +1777,15 @@
       <c r="R35" s="15"/>
     </row>
     <row r="36" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="23">
+      <c r="A36" s="8">
         <v>29</v>
       </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="37"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
@@ -1810,15 +1799,15 @@
       <c r="R36" s="15"/>
     </row>
     <row r="37" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="23">
+      <c r="A37" s="8">
         <v>30</v>
       </c>
-      <c r="B37" s="35"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="37"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="18"/>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
@@ -1832,15 +1821,15 @@
       <c r="R37" s="15"/>
     </row>
     <row r="38" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="23">
+      <c r="A38" s="8">
         <v>31</v>
       </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="37"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="18"/>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
@@ -1854,274 +1843,261 @@
       <c r="R38" s="15"/>
     </row>
     <row r="39" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
     </row>
     <row r="40" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="42" t="s">
+      <c r="A40" s="6"/>
+      <c r="B40" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="42" t="s">
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L40" s="42"/>
-      <c r="M40" s="42"/>
-      <c r="N40" s="42"/>
-      <c r="O40" s="42"/>
-      <c r="P40" s="42"/>
-      <c r="Q40" s="42"/>
-      <c r="R40" s="8"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
+      <c r="R40" s="6"/>
     </row>
     <row r="41" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="8"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
     </row>
     <row r="42" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
     </row>
     <row r="43" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="43"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="43"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
     </row>
     <row r="44" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="8" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="44" t="s">
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L44" s="45" t="s">
+      <c r="L44" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="8" t="s">
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="R44" s="8"/>
+      <c r="R44" s="6"/>
     </row>
     <row r="45" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="42" t="s">
+      <c r="A45" s="6"/>
+      <c r="B45" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="42" t="s">
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="42"/>
-      <c r="N45" s="42"/>
-      <c r="O45" s="42"/>
-      <c r="P45" s="42"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6"/>
     </row>
     <row r="46" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="46" t="s">
+      <c r="A46" s="6"/>
+      <c r="B46" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="46" t="s">
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="M46" s="42"/>
-      <c r="N46" s="42"/>
-      <c r="O46" s="42"/>
-      <c r="P46" s="42"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="162">
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="L43:P43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="L44:P44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="K40:Q40"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="B20:G20"/>
+  <mergeCells count="181">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:R7"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:R17"/>
     <mergeCell ref="H20:K20"/>
     <mergeCell ref="L20:N20"/>
     <mergeCell ref="O20:R20"/>
-    <mergeCell ref="B21:G21"/>
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="L21:N21"/>
     <mergeCell ref="O21:R21"/>
@@ -2134,74 +2110,107 @@
     <mergeCell ref="H19:K19"/>
     <mergeCell ref="L19:N19"/>
     <mergeCell ref="O19:R19"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:R7"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="L43:P43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="L44:P44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="K40:Q40"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:G38"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/รายงานปฏิบัติงาน.xlsx
+++ b/รายงานปฏิบัติงาน.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78381EE8-E96A-48FD-BEEA-7977A83D9061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CAEBD0-CCD2-42A7-9957-09F5AA9E9AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E913D3C6-8093-4C01-A734-76B2ECFA7B3E}"/>
   </bookViews>
@@ -247,17 +247,6 @@
       <top/>
       <bottom style="dotted">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -359,6 +348,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -386,15 +384,90 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -404,85 +477,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -897,26 +895,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
     </row>
     <row r="2" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -927,19 +925,19 @@
       <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="12">
         <v>2569</v>
       </c>
-      <c r="M2" s="35"/>
+      <c r="M2" s="12"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -970,53 +968,53 @@
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="36"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="37"/>
+      <c r="K4" s="14"/>
       <c r="L4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="M4" s="2"/>
-      <c r="N4" s="38" t="s">
+      <c r="N4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="38"/>
+      <c r="O4" s="15"/>
       <c r="P4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="39"/>
+      <c r="R4" s="16"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="40" t="s">
+      <c r="E5" s="40" t="s">
         <v>41</v>
       </c>
+      <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1029,818 +1027,818 @@
       <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15" t="s">
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="32" t="s">
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="15" t="s">
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="33" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
     </row>
     <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>1</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="15" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="26" t="s">
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>2</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="15" t="s">
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="26" t="s">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="16" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="15" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="26" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="15" t="s">
+      <c r="F11" s="24"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>6</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="27">
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="26">
         <v>18</v>
       </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="15" t="s">
+      <c r="F12" s="27"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>6</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>6</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="27">
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="26">
         <v>18</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="15" t="s">
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
     </row>
     <row r="14" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>7</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>6</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="27">
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="26">
         <v>18</v>
       </c>
-      <c r="F14" s="28"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="15" t="s">
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>8</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="30">
         <v>6</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24">
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30">
         <v>18</v>
       </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="15" t="s">
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>9</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="30">
         <v>0</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24">
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30">
         <v>12</v>
       </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="15" t="s">
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="21"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="34"/>
     </row>
     <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>10</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="16" t="s">
+      <c r="C17" s="21"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="15" t="s">
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="21"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="34"/>
     </row>
     <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>11</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="16" t="s">
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="15" t="s">
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="21"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="34"/>
     </row>
     <row r="19" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>12</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="34"/>
     </row>
     <row r="20" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>13</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
     </row>
     <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>14</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
     </row>
     <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>15</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="21"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="34"/>
     </row>
     <row r="23" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>16</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="21"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="34"/>
     </row>
     <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>17</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
     </row>
     <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>18</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
     </row>
     <row r="26" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>19</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="21"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="34"/>
     </row>
     <row r="27" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>20</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="21"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="34"/>
     </row>
     <row r="28" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>21</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
     </row>
     <row r="29" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>22</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="21"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="34"/>
     </row>
     <row r="30" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>23</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="21"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="34"/>
     </row>
     <row r="31" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>24</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
     </row>
     <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>25</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
     </row>
     <row r="33" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>26</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
     </row>
     <row r="34" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>27</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
     </row>
     <row r="35" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>28</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
     </row>
     <row r="36" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>29</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
     </row>
     <row r="37" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>30</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
     </row>
     <row r="38" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>31</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
     </row>
     <row r="39" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
@@ -1864,26 +1862,26 @@
     </row>
     <row r="40" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="12" t="s">
+      <c r="K40" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
+      <c r="L40" s="37"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="37"/>
+      <c r="O40" s="37"/>
+      <c r="P40" s="37"/>
+      <c r="Q40" s="37"/>
       <c r="R40" s="6"/>
     </row>
     <row r="41" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1928,21 +1926,21 @@
     </row>
     <row r="43" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="6"/>
     </row>
@@ -1950,13 +1948,13 @@
       <c r="A44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="6" t="s">
         <v>28</v>
       </c>
@@ -1966,13 +1964,13 @@
       <c r="K44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L44" s="14" t="s">
+      <c r="L44" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
+      <c r="M44" s="39"/>
+      <c r="N44" s="39"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="39"/>
       <c r="Q44" s="6" t="s">
         <v>28</v>
       </c>
@@ -1980,116 +1978,150 @@
     </row>
     <row r="45" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
-      <c r="L45" s="12" t="s">
+      <c r="L45" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
+      <c r="M45" s="37"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="37"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="6"/>
     </row>
     <row r="46" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="37"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="37"/>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="181">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="H6:K7"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:R7"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="L43:P43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="L44:P44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="K40:Q40"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="H17:K17"/>
@@ -2114,101 +2146,67 @@
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="E21:G21"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="L43:P43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="L44:P44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="K40:Q40"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="H6:K7"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:R7"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="Q4:R4"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
